--- a/static/kangming/出口报关单模板.xlsx
+++ b/static/kangming/出口报关单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haoya/Downloads/kangming-final-correct/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A75D02-2012-1A4E-BC63-F138386B677D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8E7940-2194-E24B-8BBE-E4036BFFFBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,12 +728,12 @@
     <col min="3" max="3" width="23.1640625" customWidth="1"/>
     <col min="4" max="4" width="17.1640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.5" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.1640625" customWidth="1"/>
-    <col min="10" max="10" width="19.5" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" customWidth="1"/>
+    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" customHeight="1">

--- a/static/kangming/出口报关单模板.xlsx
+++ b/static/kangming/出口报关单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haoya/Downloads/kangming-final-correct/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8E7940-2194-E24B-8BBE-E4036BFFFBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A75D02-2012-1A4E-BC63-F138386B677D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,12 +728,12 @@
     <col min="3" max="3" width="23.1640625" customWidth="1"/>
     <col min="4" max="4" width="17.1640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" customWidth="1"/>
-    <col min="9" max="9" width="19.5" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.1640625" customWidth="1"/>
+    <col min="10" max="10" width="19.5" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" customHeight="1">
